--- a/docs/narrative/entrega_escritor_gvo_v1/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO_PARA_ESCRITOR.xlsx
+++ b/docs/narrative/entrega_escritor_gvo_v1/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO_PARA_ESCRITOR.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R4601b69ae7054791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R0ab2cb6f57274fd7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,9 +85,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -190,6 +190,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="12" max="12" width="50" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="72" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -1092,11 +1098,15 @@
       <x:c r="K22" t="str">
         <x:v>30-80 caracteres</x:v>
       </x:c>
-      <x:c r="L22" t="str"/>
+      <x:c r="L22" t="str">
+        <x:v>Abriendo Mundo III</x:v>
+      </x:c>
       <x:c r="M22" t="str"/>
-      <x:c r="N22" t="str"/>
+      <x:c r="N22" t="str">
+        <x:v>Copy runtime definitivo; aprobación humana consolidada por GVO-017K-R1.</x:v>
+      </x:c>
       <x:c r="O22" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>FINAL / human_approved</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1133,11 +1143,15 @@
       <x:c r="K23" t="str">
         <x:v>25-70 caracteres</x:v>
       </x:c>
-      <x:c r="L23" t="str"/>
+      <x:c r="L23" t="str">
+        <x:v>Preparando el Cuaderno Pixel de Pruebas…</x:v>
+      </x:c>
       <x:c r="M23" t="str"/>
-      <x:c r="N23" t="str"/>
+      <x:c r="N23" t="str">
+        <x:v>Copy runtime definitivo; aprobación humana consolidada por GVO-017K-R1.</x:v>
+      </x:c>
       <x:c r="O23" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>FINAL / human_approved</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3556,7 +3570,7 @@
       <x:c r="M82" t="str"/>
       <x:c r="N82" t="str"/>
       <x:c r="O82" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -3597,7 +3611,7 @@
       <x:c r="M83" t="str"/>
       <x:c r="N83" t="str"/>
       <x:c r="O83" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -3638,7 +3652,7 @@
       <x:c r="M84" t="str"/>
       <x:c r="N84" t="str"/>
       <x:c r="O84" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3679,7 +3693,7 @@
       <x:c r="M85" t="str"/>
       <x:c r="N85" t="str"/>
       <x:c r="O85" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3720,7 +3734,7 @@
       <x:c r="M86" t="str"/>
       <x:c r="N86" t="str"/>
       <x:c r="O86" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3761,7 +3775,7 @@
       <x:c r="M87" t="str"/>
       <x:c r="N87" t="str"/>
       <x:c r="O87" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3802,7 +3816,7 @@
       <x:c r="M88" t="str"/>
       <x:c r="N88" t="str"/>
       <x:c r="O88" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3843,7 +3857,7 @@
       <x:c r="M89" t="str"/>
       <x:c r="N89" t="str"/>
       <x:c r="O89" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3884,7 +3898,7 @@
       <x:c r="M90" t="str"/>
       <x:c r="N90" t="str"/>
       <x:c r="O90" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3925,7 +3939,7 @@
       <x:c r="M91" t="str"/>
       <x:c r="N91" t="str"/>
       <x:c r="O91" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3966,7 +3980,7 @@
       <x:c r="M92" t="str"/>
       <x:c r="N92" t="str"/>
       <x:c r="O92" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -4007,7 +4021,7 @@
       <x:c r="M93" t="str"/>
       <x:c r="N93" t="str"/>
       <x:c r="O93" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -4048,7 +4062,7 @@
       <x:c r="M94" t="str"/>
       <x:c r="N94" t="str"/>
       <x:c r="O94" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4089,7 +4103,7 @@
       <x:c r="M95" t="str"/>
       <x:c r="N95" t="str"/>
       <x:c r="O95" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -4130,7 +4144,7 @@
       <x:c r="M96" t="str"/>
       <x:c r="N96" t="str"/>
       <x:c r="O96" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4171,7 +4185,7 @@
       <x:c r="M97" t="str"/>
       <x:c r="N97" t="str"/>
       <x:c r="O97" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4212,7 +4226,7 @@
       <x:c r="M98" t="str"/>
       <x:c r="N98" t="str"/>
       <x:c r="O98" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -4253,7 +4267,7 @@
       <x:c r="M99" t="str"/>
       <x:c r="N99" t="str"/>
       <x:c r="O99" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4294,7 +4308,7 @@
       <x:c r="M100" t="str"/>
       <x:c r="N100" t="str"/>
       <x:c r="O100" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -4335,7 +4349,7 @@
       <x:c r="M101" t="str"/>
       <x:c r="N101" t="str"/>
       <x:c r="O101" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -4376,7 +4390,7 @@
       <x:c r="M102" t="str"/>
       <x:c r="N102" t="str"/>
       <x:c r="O102" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -4417,7 +4431,7 @@
       <x:c r="M103" t="str"/>
       <x:c r="N103" t="str"/>
       <x:c r="O103" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -4458,7 +4472,7 @@
       <x:c r="M104" t="str"/>
       <x:c r="N104" t="str"/>
       <x:c r="O104" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
